--- a/Data/Output_Results.xlsx
+++ b/Data/Output_Results.xlsx
@@ -183,6 +183,12 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">DepartureCity missing; Passengers invalid; TotalBudget invalid; DepartureDate in the past; ReturnDate in the past; TransportPreference invalid; </x:t>
+  </x:si>
+  <x:si>
+    <x:t>No weather data</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Insufficient data</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -729,10 +735,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:14">
@@ -773,10 +779,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:14">
@@ -817,10 +823,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:14">
@@ -861,10 +867,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/Output_Results.xlsx
+++ b/Data/Output_Results.xlsx
@@ -10,7 +10,6 @@
     <x:sheet name="Accommodation" sheetId="2" r:id="rId5"/>
     <x:sheet name="Weather" sheetId="3" r:id="rId7"/>
     <x:sheet name="Summary" sheetId="4" r:id="rId8"/>
-    <x:sheet name="Errors" sheetId="5" r:id="rId9"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
@@ -44,6 +43,30 @@
     <x:t>BookingLink</x:t>
   </x:si>
   <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Zbor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wizz Air</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10:05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11:10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2 hr 5 min</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RON 376</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.google.com/travel/flights?q=Bucuresti%20to%20Roma%2010%20Feb%202026</x:t>
+  </x:si>
+  <x:si>
     <x:t>AccommodationType</x:t>
   </x:si>
   <x:si>
@@ -56,6 +79,2055 @@
     <x:t>Rating</x:t>
   </x:si>
   <x:si>
+    <x:t>G55 Design Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/g55-design.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=1&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=259077901_104589657_2_34_0&amp;highlighted_blocks=259077901_104589657_2_34_0&amp;matching_block_id=259077901_104589657_2_34_0&amp;sr_pri_blocks=259077901_104589657_2_34_0__80500&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 805</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Superior Double Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Principe Di Piemonte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/principe-di-piemonte-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=2&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=19093801_406887697_2_2_0&amp;highlighted_blocks=19093801_406887697_2_2_0&amp;matching_block_id=19093801_406887697_2_2_0&amp;sr_pri_blocks=19093801_406887697_2_2_0__37500&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 375</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Double or Twin Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Albergo Enrica</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/albergo-enrica.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=3&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=27877912_365274067_2_0_0&amp;highlighted_blocks=27877912_365274067_2_0_0&amp;matching_block_id=27877912_365274067_2_0_0&amp;sr_pri_blocks=27877912_365274067_2_0_0__40000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 400</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Small Double Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Venustas Roma Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/venustas-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=4&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=252719202_103822780_0_0_0&amp;highlighted_blocks=252719202_103822780_0_0_0&amp;matching_block_id=252719202_103822780_0_0_0&amp;sr_pri_blocks=252719202_103822780_0_0_0__47979&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 480</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Twin Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mascagni Luxury Rooms &amp; Suites</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/mascagni-dependance.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=5&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=174227602_90590428_2_1_0&amp;highlighted_blocks=174227602_90590428_2_1_0&amp;matching_block_id=174227602_90590428_2_1_0&amp;sr_pri_blocks=174227602_90590428_2_1_0__92340&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 923</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Premium Double or Twin Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aparthotel Colombo Roma</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/residence-colombo-112.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=6&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=2894319_95153034_2_2_0&amp;highlighted_blocks=2894319_95153034_2_2_0&amp;matching_block_id=2894319_95153034_2_2_0&amp;sr_pri_blocks=2894319_95153034_2_2_0__45936&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 459</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standard Double Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Novecento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/novecento-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=7&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=8441602_0_2_1_0&amp;highlighted_blocks=8441602_0_2_1_0&amp;matching_block_id=8441602_0_2_1_0&amp;sr_pri_blocks=8441602_0_2_1_0__43601&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 436</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Re Di Roma</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/re-di-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=8&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=8917502_406798409_2_1_0&amp;highlighted_blocks=8917502_406798409_2_1_0&amp;matching_block_id=8917502_406798409_2_1_0&amp;sr_pri_blocks=8917502_406798409_2_1_0__62500&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 625</x:t>
+  </x:si>
+  <x:si>
+    <x:t>River Palace Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/riverpalacehotel.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=9&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=0_0_2_0_0&amp;highlighted_blocks=0_0_2_0_0&amp;matching_block_id=0_0_2_0_0&amp;sr_pri_blocks=0_0_2_0_0__67481&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 675</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room Assigned on Arrival</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CC Palace Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/cc-palace-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=10&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=932390414_0_2_0_0&amp;highlighted_blocks=932390414_0_2_0_0&amp;matching_block_id=932390414_0_2_0_0&amp;sr_pri_blocks=932390414_0_2_0_0__116999&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,170</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Economy Double Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Massimi City Garden</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/massimi-city-garden.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=11&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=1150547901_387861668_2_1_0&amp;highlighted_blocks=1150547901_387861668_2_1_0&amp;matching_block_id=1150547901_387861668_2_1_0&amp;sr_pri_blocks=1150547901_387861668_2_1_0__52736&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 527</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standard Double or Twin Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Albergo Etico Roma</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/albergo-etico-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=12&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=442792001_132483454_0_1_0&amp;highlighted_blocks=442792001_132483454_0_1_0&amp;matching_block_id=442792001_132483454_0_1_0&amp;sr_pri_blocks=442792001_132483454_0_1_0__72794&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 728</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Double Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Aurelius</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/aurelius-art-gallery-hotel.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=13&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=8340108_365537998_0_0_0&amp;highlighted_blocks=8340108_365537998_0_0_0&amp;matching_block_id=8340108_365537998_0_0_0&amp;sr_pri_blocks=8340108_365537998_0_0_0__41701&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 417</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dotcampus Roma City Center</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/keyz-docampus-roma-san-giovanni.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=14&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=982502004_370504597_0_2_0&amp;highlighted_blocks=982502004_370504597_0_2_0&amp;matching_block_id=982502004_370504597_0_2_0&amp;sr_pri_blocks=982502004_370504597_0_2_0__55200&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 552</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Deluxe Double Room with Balcony</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Pacific</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/pacific.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=15&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=1904116_0_2_1_0&amp;highlighted_blocks=1904116_0_2_1_0&amp;matching_block_id=1904116_0_2_1_0&amp;sr_pri_blocks=1904116_0_2_1_0__64466&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 645</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ruby Giulia Hotel Rome</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/ruby-giulia-rome.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=16&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=1518262602_425724673_2_2_0&amp;highlighted_blocks=1518262602_425724673_2_2_0&amp;matching_block_id=1518262602_425724673_2_2_0&amp;sr_pri_blocks=1518262602_425724673_2_2_0__93412&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 934</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lovely</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Boutique Hotel Atelier '800</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/900-liberty.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=17&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=129697016_88478484_0_0_0&amp;highlighted_blocks=129697016_88478484_0_0_0&amp;matching_block_id=129697016_88478484_0_0_0&amp;sr_pri_blocks=129697016_88478484_0_0_0__84300&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 843</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Superior Double or Twin Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Santa Prisca</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/santa-prisca.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=18&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=28918617_165295148_2_1_0&amp;highlighted_blocks=28918617_165295148_2_1_0&amp;matching_block_id=28918617_165295148_2_1_0&amp;sr_pri_blocks=28918617_165295148_2_1_0__60439&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 604</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Precise House Mantegna Roma</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/precise-mantegna.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=19&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=0_0_2_0_0&amp;highlighted_blocks=0_0_2_0_0&amp;matching_block_id=0_0_2_0_0&amp;sr_pri_blocks=0_0_2_0_0__53073&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 531</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Barrett</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/pensione-barrett.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=20&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=220283302_97914042_2_1_0_832399&amp;highlighted_blocks=220283302_97914042_2_1_0_832399&amp;matching_block_id=220283302_97914042_2_1_0_832399&amp;sr_pri_blocks=220283302_97914042_2_1_0_832399_97503&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 975</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Milton Roma</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/best-western-plus-hotel-milton.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=21&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=8371408_94109566_2_1_0&amp;highlighted_blocks=8371408_94109566_2_1_0&amp;matching_block_id=8371408_94109566_2_1_0&amp;sr_pri_blocks=8371408_94109566_2_1_0__93857&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Adesso Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/adesso-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=22&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=0_0_2_0_0&amp;highlighted_blocks=0_0_2_0_0&amp;matching_block_id=0_0_2_0_0&amp;sr_pri_blocks=0_0_2_0_0__59488&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 595</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Magic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/magic.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=23&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=8441303_88158145_3_0_0&amp;highlighted_blocks=8441303_88158145_3_0_0&amp;matching_block_id=8441303_88158145_3_0_0&amp;sr_pri_blocks=8441303_88158145_3_0_0__54217&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 542</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Classic Triple Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The Boutique Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/joli-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=24&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=0_0_2_0_0&amp;highlighted_blocks=0_0_2_0_0&amp;matching_block_id=0_0_2_0_0&amp;sr_pri_blocks=0_0_2_0_0__70885&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 709</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Classic Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>c-hotels Club House Roma</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/club-house-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=25&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=8103001_0_2_0_0&amp;highlighted_blocks=8103001_0_2_0_0&amp;matching_block_id=8103001_0_2_0_0&amp;sr_pri_blocks=8103001_0_2_0_0__48313&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 483</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Smart Double Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Ottaviano Augusto</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/ottaviano-augusto-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=26&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026355&amp;all_sr_blocks=826568310_0_2_1_0&amp;highlighted_blocks=826568310_0_2_1_0&amp;matching_block_id=826568310_0_2_1_0&amp;sr_pri_blocks=826568310_0_2_1_0__67232&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 672</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Twin Room - Disability Access</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Radio Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/radio-hotel.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=27&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026355&amp;all_sr_blocks=82764612_88175806_0_2_0_519122&amp;highlighted_blocks=82764612_88175806_0_2_0_519122&amp;matching_block_id=82764612_88175806_0_2_0_519122&amp;sr_pri_blocks=82764612_88175806_0_2_0_519122_33500&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 335</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FH55 Grand Hotel Palatino</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/gandhtelplatino.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=28&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026355&amp;all_sr_blocks=8073207_0_2_0_0&amp;highlighted_blocks=8073207_0_2_0_0&amp;matching_block_id=8073207_0_2_0_0&amp;sr_pri_blocks=8073207_0_2_0_0__122366&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,224</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Classic Double Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Kent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotelkentroma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=29&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026355&amp;all_sr_blocks=8122008_0_2_0_0&amp;highlighted_blocks=8122008_0_2_0_0&amp;matching_block_id=8122008_0_2_0_0&amp;sr_pri_blocks=8122008_0_2_0_0__36780&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 368</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lilium Boutique Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/liliumhotelroma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=30&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026355&amp;all_sr_blocks=8077502_0_2_0_0&amp;highlighted_blocks=8077502_0_2_0_0&amp;matching_block_id=8077502_0_2_0_0&amp;sr_pri_blocks=8077502_0_2_0_0__65821&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 658</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The Hoxton, Rome</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/the-hoxton-rome.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=31&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026355&amp;all_sr_blocks=711865502_296760977_0_0_0&amp;highlighted_blocks=711865502_296760977_0_0_0&amp;matching_block_id=711865502_296760977_0_0_0&amp;sr_pri_blocks=711865502_296760977_0_0_0__111793&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cozy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LE RÊVE DE NAIM Roma</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/spagna-royal-suite.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=32&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026355&amp;all_sr_blocks=25618523_0_2_0_0&amp;highlighted_blocks=25618523_0_2_0_0&amp;matching_block_id=25618523_0_2_0_0&amp;sr_pri_blocks=25618523_0_2_0_0__80188&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 802</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Morgana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotelmorganaroma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=33&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026355&amp;all_sr_blocks=8064921_0_2_0_0&amp;highlighted_blocks=8064921_0_2_0_0&amp;matching_block_id=8064921_0_2_0_0&amp;sr_pri_blocks=8064921_0_2_0_0__73934&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 739</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel St Martin by OMNIA hotels</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/st-martin-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=34&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026355&amp;all_sr_blocks=617179904_0_2_0_0&amp;highlighted_blocks=617179904_0_2_0_0&amp;matching_block_id=617179904_0_2_0_0&amp;sr_pri_blocks=617179904_0_2_0_0__70717&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 707</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Queen Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Donna Laura Palace by OMNIA hotels</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/donnalaurapalace.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=35&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026355&amp;all_sr_blocks=8029238_0_2_0_0&amp;highlighted_blocks=8029238_0_2_0_0&amp;matching_block_id=8029238_0_2_0_0&amp;sr_pri_blocks=8029238_0_2_0_0__59350&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 594</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Montecarlo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/montecarlo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=36&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026355&amp;all_sr_blocks=8195610_402982406_0_33_0&amp;highlighted_blocks=8195610_402982406_0_33_0&amp;matching_block_id=8195610_402982406_0_33_0&amp;sr_pri_blocks=8195610_402982406_0_33_0__75690&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 757</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comfort Double or Twin Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Roma Vaticano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hrv-deluxe.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=37&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026355&amp;all_sr_blocks=461051301_140591961_2_0_0_1081572&amp;highlighted_blocks=461051301_140591961_2_0_0_1081572&amp;matching_block_id=461051301_140591961_2_0_0_1081572&amp;sr_pri_blocks=461051301_140591961_2_0_0_1081572_71063&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 711</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Deluxe Double or Twin Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Albani Hotel Roma</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/albani-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=38&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026355&amp;all_sr_blocks=8310802_0_2_0_0&amp;highlighted_blocks=8310802_0_2_0_0&amp;matching_block_id=8310802_0_2_0_0&amp;sr_pri_blocks=8310802_0_2_0_0__59357&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Classic Double or Twin Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Occidental Aran Park</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/aran-park.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=39&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026355&amp;all_sr_blocks=8462205_264874520_2_34_0_341227&amp;highlighted_blocks=8462205_264874520_2_34_0_341227&amp;matching_block_id=8462205_264874520_2_34_0_341227&amp;sr_pri_blocks=8462205_264874520_2_34_0_341227_36620&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 366</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Superior Double or Twin Room with Balcony</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACA Hotel Viminale</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/aca-viminale.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=40&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026355&amp;all_sr_blocks=1348523902_407528853_0_0_0_790032&amp;highlighted_blocks=1348523902_407528853_0_0_0_790032&amp;matching_block_id=1348523902_407528853_0_0_0_790032&amp;sr_pri_blocks=1348523902_407528853_0_0_0_790032_101702&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Monti 66 Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/monti-66.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=41&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026355&amp;all_sr_blocks=1002660103_373056001_2_0_0&amp;highlighted_blocks=1002660103_373056001_2_0_0&amp;matching_block_id=1002660103_373056001_2_0_0&amp;sr_pri_blocks=1002660103_373056001_2_0_0__82203&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 822</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Triple Room with City View</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trastevere Roma | UNA Esperienze</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/unahotels-trastevere-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=42&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026355&amp;all_sr_blocks=804937501_0_2_0_0&amp;highlighted_blocks=804937501_0_2_0_0&amp;matching_block_id=804937501_0_2_0_0&amp;sr_pri_blocks=804937501_0_2_0_0__100703&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Bella Vita</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/bella-vita-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=43&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026355&amp;all_sr_blocks=162305401_145616090_0_2_0&amp;highlighted_blocks=162305401_145616090_0_2_0&amp;matching_block_id=162305401_145616090_0_2_0&amp;sr_pri_blocks=162305401_145616090_0_2_0__33421&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 334</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Double Room with Private Bathroom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lumi Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/lumi-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=44&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026355&amp;all_sr_blocks=1301733406_405923378_0_0_0&amp;highlighted_blocks=1301733406_405923378_0_0_0&amp;matching_block_id=1301733406_405923378_0_0_0&amp;sr_pri_blocks=1301733406_405923378_0_0_0__71500&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 715</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Superior Double or Twin Room with City View</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Abitart</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/abitart-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=45&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026355&amp;all_sr_blocks=8459402_365585155_0_1_0&amp;highlighted_blocks=8459402_365585155_0_1_0&amp;matching_block_id=8459402_365585155_0_1_0&amp;sr_pri_blocks=8459402_365585155_0_1_0__79700&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 797</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Barberini Retreat Boutique Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/barberini-retreat.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=46&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026355&amp;all_sr_blocks=1224835802_394585415_2_0_0&amp;highlighted_blocks=1224835802_394585415_2_0_0&amp;matching_block_id=1224835802_394585415_2_0_0&amp;sr_pri_blocks=1224835802_394585415_2_0_0__77637&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 776</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Del Corso</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/delcorsoroma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=47&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026355&amp;all_sr_blocks=0_0_2_0_0&amp;highlighted_blocks=0_0_2_0_0&amp;matching_block_id=0_0_2_0_0&amp;sr_pri_blocks=0_0_2_0_0__61136&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 611</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MF Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/m-f.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=48&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026355&amp;all_sr_blocks=49675323_91254283_0_2_0_519127&amp;highlighted_blocks=49675323_91254283_0_2_0_519127&amp;matching_block_id=49675323_91254283_0_2_0_519127&amp;sr_pri_blocks=49675323_91254283_0_2_0_519127_38713&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 387</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Pisa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/pisa-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=49&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026355&amp;all_sr_blocks=54412419_88465807_0_0_0&amp;highlighted_blocks=54412419_88465807_0_0_0&amp;matching_block_id=54412419_88465807_0_0_0&amp;sr_pri_blocks=54412419_88465807_0_0_0__41627&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 416</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Caracciolo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/caracciolo-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=50&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=8471201_0_2_0_0&amp;highlighted_blocks=8471201_0_2_0_0&amp;matching_block_id=8471201_0_2_0_0&amp;sr_pri_blocks=8471201_0_2_0_0__40190&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 402</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J Maluni City Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/j-maluni-city-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=51&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=1256043101_398142412_2_2_0&amp;highlighted_blocks=1256043101_398142412_2_2_0&amp;matching_block_id=1256043101_398142412_2_2_0&amp;sr_pri_blocks=1256043101_398142412_2_2_0__58702&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 587</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cloud 9 Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/cloud-9-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=52&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=1043076601_376700122_2_0_0_722471&amp;highlighted_blocks=1043076601_376700122_2_0_0_722471&amp;matching_block_id=1043076601_376700122_2_0_0_722471&amp;sr_pri_blocks=1043076601_376700122_2_0_0_722471_65071&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 651</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Exe Domus Aurea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/exedomusaurea.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=53&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=8024501_0_2_0_0&amp;highlighted_blocks=8024501_0_2_0_0&amp;matching_block_id=8024501_0_2_0_0&amp;sr_pri_blocks=8024501_0_2_0_0__66103&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 661</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Giolli Nazionale</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/giolli.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=54&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=8882174_0_2_0_0&amp;highlighted_blocks=8882174_0_2_0_0&amp;matching_block_id=8882174_0_2_0_0&amp;sr_pri_blocks=8882174_0_2_0_0__84477&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 845</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Small Double or Twin Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Domus Mea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/domus-mea.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=55&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=8323510_88054374_0_0_0_373958&amp;highlighted_blocks=8323510_88054374_0_0_0_373958&amp;matching_block_id=8323510_88054374_0_0_0_373958&amp;sr_pri_blocks=8323510_88054374_0_0_0_373958_62810&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 628</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The Britannia Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/britannia-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=56&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=0_0_2_0_0&amp;highlighted_blocks=0_0_2_0_0&amp;matching_block_id=0_0_2_0_0&amp;sr_pri_blocks=0_0_2_0_0__85923&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 859</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Basic Double Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Cristoforo Colombo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/cristoforo-colombo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=57&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=4676802_91422788_0_1_0&amp;highlighted_blocks=4676802_91422788_0_1_0&amp;matching_block_id=4676802_91422788_0_1_0&amp;sr_pri_blocks=4676802_91422788_0_1_0__46561&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 466</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Triple Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Alexis</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/accommodation-planet-29.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=58&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=25194801_88164463_2_2_0_557976&amp;highlighted_blocks=25194801_88164463_2_2_0_557976&amp;matching_block_id=25194801_88164463_2_2_0_557976&amp;sr_pri_blocks=25194801_88164463_2_2_0_557976_47947&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 479</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Double or Twin Room with Private Bathroom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Orazia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/orazia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=59&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=8987903_0_2_0_0&amp;highlighted_blocks=8987903_0_2_0_0&amp;matching_block_id=8987903_0_2_0_0&amp;sr_pri_blocks=8987903_0_2_0_0__56741&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 567</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Nova Domus Aurelia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/nova-domus-aurelia-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=60&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=800204001_0_2_1_0&amp;highlighted_blocks=800204001_0_2_1_0&amp;matching_block_id=800204001_0_2_1_0&amp;sr_pri_blocks=800204001_0_2_1_0__56658&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Boutique Hotel Galatea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/galatea.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=61&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=8664608_88159909_2_2_0&amp;highlighted_blocks=8664608_88159909_2_2_0&amp;matching_block_id=8664608_88159909_2_2_0&amp;sr_pri_blocks=8664608_88159909_2_2_0__88074&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 881</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Pulitzer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/pulitzer.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=62&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=8903505_93708641_2_2_0&amp;highlighted_blocks=8903505_93708641_2_2_0&amp;matching_block_id=8903505_93708641_2_2_0&amp;sr_pri_blocks=8903505_93708641_2_2_0__53947&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 539</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Emona Aquaeductus</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/emona-aquaeductus.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=63&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=8941515_0_2_0_0&amp;highlighted_blocks=8941515_0_2_0_0&amp;matching_block_id=8941515_0_2_0_0&amp;sr_pri_blocks=8941515_0_2_0_0__60217&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 602</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The Spring House Hotel Rome Vatican, Tapestry Collection Hilton</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/springhouseroma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=64&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=8135249_403129460_2_2_0&amp;highlighted_blocks=8135249_403129460_2_2_0&amp;matching_block_id=8135249_403129460_2_2_0&amp;sr_pri_blocks=8135249_403129460_2_2_0__94640&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 946</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Glam Luxury Rome</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/glam-luxury-rome.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=65&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=999070201_372738777_2_0_0&amp;highlighted_blocks=999070201_372738777_2_0_0&amp;matching_block_id=999070201_372738777_2_0_0&amp;sr_pri_blocks=999070201_372738777_2_0_0__79555&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 796</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Suite with Balcony</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel OKAPI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/okapi-rooms.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=66&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=18755201_88162253_2_1_0&amp;highlighted_blocks=18755201_88162253_2_1_0&amp;matching_block_id=18755201_88162253_2_1_0&amp;sr_pri_blocks=18755201_88162253_2_1_0__63931&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Latinum</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/latinum.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=67&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=8798205_0_2_1_0&amp;highlighted_blocks=8798205_0_2_1_0&amp;matching_block_id=8798205_0_2_1_0&amp;sr_pri_blocks=8798205_0_2_1_0__59055&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Double or Twin Room with Extra Bed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Principessa Isabella</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/principessatea.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=68&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=8071002_0_2_1_0&amp;highlighted_blocks=8071002_0_2_1_0&amp;matching_block_id=8071002_0_2_1_0&amp;sr_pri_blocks=8071002_0_2_1_0__61930&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 619</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Duca d'Alba Hotel - Chateaux &amp; Hotels Collection</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/duca-d-alba.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=69&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=0_0_2_0_0&amp;highlighted_blocks=0_0_2_0_0&amp;matching_block_id=0_0_2_0_0&amp;sr_pri_blocks=0_0_2_0_0__77414&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROME'S GLORIA HOTEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/romes-gloria.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=70&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=1122723206_385023549_2_0_0&amp;highlighted_blocks=1122723206_385023549_2_0_0&amp;matching_block_id=1122723206_385023549_2_0_0&amp;sr_pri_blocks=1122723206_385023549_2_0_0__65769&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Madison Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/princemadison.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=71&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=8057803_88153624_2_2_0&amp;highlighted_blocks=8057803_88153624_2_2_0&amp;matching_block_id=8057803_88153624_2_2_0&amp;sr_pri_blocks=8057803_88153624_2_2_0__62669&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 627</x:t>
+  </x:si>
+  <x:si>
+    <x:t>room Select Via Veneto</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/veneto-rome.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=72&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=8345502_0_2_0_0&amp;highlighted_blocks=8345502_0_2_0_0&amp;matching_block_id=8345502_0_2_0_0&amp;sr_pri_blocks=8345502_0_2_0_0__65753&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Metropolis</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/metropolis.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=73&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=24396401_0_2_1_0&amp;highlighted_blocks=24396401_0_2_1_0&amp;matching_block_id=24396401_0_2_1_0&amp;sr_pri_blocks=24396401_0_2_1_0__68171&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 682</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Orazio Palace Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/opalace.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=74&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026356&amp;all_sr_blocks=183150502_91628377_0_1_0&amp;highlighted_blocks=183150502_91628377_0_1_0&amp;matching_block_id=183150502_91628377_0_1_0&amp;sr_pri_blocks=183150502_91628377_0_1_0__119995&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The Social Hub Rome</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/the-social-hub-rome.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=75&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=1310660006_403842865_0_2_0_853475&amp;highlighted_blocks=1310660006_403842865_0_2_0_853475&amp;matching_block_id=1310660006_403842865_0_2_0_853475&amp;sr_pri_blocks=1310660006_403842865_0_2_0_853475_60255&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 603</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Superior Queen Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Albergo Delle Regioni, Barberini - Fontana di Trevi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/albergo-delle-regioni.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=76&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=392044903_418099493_0_0_0&amp;highlighted_blocks=392044903_418099493_0_0_0&amp;matching_block_id=392044903_418099493_0_0_0&amp;sr_pri_blocks=392044903_418099493_0_0_0__97008&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 970</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel St. Moritz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/st-moritz.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=77&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=8777802_0_2_1_0&amp;highlighted_blocks=8777802_0_2_1_0&amp;matching_block_id=8777802_0_2_1_0&amp;sr_pri_blocks=8777802_0_2_1_0__71623&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 716</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cardinal Hotel St. Peter</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/cardinal-saint-peter.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=78&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=8873509_94301762_2_1_0_82021&amp;highlighted_blocks=8873509_94301762_2_1_0_82021&amp;matching_block_id=8873509_94301762_2_1_0_82021&amp;sr_pri_blocks=8873509_94301762_2_1_0_82021_50853&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Imperiale by OMNIA hotels</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/imperiale.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=79&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=8951502_88441036_2_0_0&amp;highlighted_blocks=8951502_88441036_2_0_0&amp;matching_block_id=8951502_88441036_2_0_0&amp;sr_pri_blocks=8951502_88441036_2_0_0__116068&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,161</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Canova</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/canova.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=80&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=0_0_2_0_0&amp;highlighted_blocks=0_0_2_0_0&amp;matching_block_id=0_0_2_0_0&amp;sr_pri_blocks=0_0_2_0_0__55891&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 559</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH Collection Roma Centro</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/nh-roma-leonardo-da-vinci.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=81&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=8045307_94109198_0_2_0&amp;highlighted_blocks=8045307_94109198_0_2_0&amp;matching_block_id=8045307_94109198_0_2_0&amp;sr_pri_blocks=8045307_94109198_0_2_0__101000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel dei Barbieri</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/dei-barbieri.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=82&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=222913201_98460978_2_2_0&amp;highlighted_blocks=222913201_98460978_2_2_0&amp;matching_block_id=222913201_98460978_2_2_0&amp;sr_pri_blocks=222913201_98460978_2_2_0__139388&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,394</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Colosseum</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotelcolosseum.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=83&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=8299502_0_2_1_0&amp;highlighted_blocks=8299502_0_2_1_0&amp;matching_block_id=8299502_0_2_1_0&amp;sr_pri_blocks=8299502_0_2_1_0__97453&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Virginia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotelvirginiaroma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=84&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=8083401_0_2_0_0&amp;highlighted_blocks=8083401_0_2_0_0&amp;matching_block_id=8083401_0_2_0_0&amp;sr_pri_blocks=8083401_0_2_0_0__47684&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 477</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mangili Garden Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/garden-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=85&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=0_0_2_1_0&amp;highlighted_blocks=0_0_2_1_0&amp;matching_block_id=0_0_2_1_0&amp;sr_pri_blocks=0_0_2_1_0__67364&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 674</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Deluxe Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>c-hotels Fiume</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/fiumeroma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=86&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=8103101_0_2_0_0&amp;highlighted_blocks=8103101_0_2_0_0&amp;matching_block_id=8103101_0_2_0_0&amp;sr_pri_blocks=8103101_0_2_0_0__61931&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Villa Zaccardi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/villa-zaccardi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=87&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=0_0_2_1_0&amp;highlighted_blocks=0_0_2_1_0&amp;matching_block_id=0_0_2_1_0&amp;sr_pri_blocks=0_0_2_1_0__56037&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 560</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Magica Luna Boutique Hotel - Roma</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/magica-luna-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=88&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=374799905_0_2_0_0&amp;highlighted_blocks=374799905_0_2_0_0&amp;matching_block_id=374799905_0_2_0_0&amp;sr_pri_blocks=374799905_0_2_0_0__84910&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 849</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Il Campo Marzio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/il-campo-marzio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=89&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=0_0_2_0_0&amp;highlighted_blocks=0_0_2_0_0&amp;matching_block_id=0_0_2_0_0&amp;sr_pri_blocks=0_0_2_0_0__102639&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Mascagni</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/mascagni.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=90&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=8004602_0_2_1_0&amp;highlighted_blocks=8004602_0_2_1_0&amp;matching_block_id=8004602_0_2_1_0&amp;sr_pri_blocks=8004602_0_2_1_0__106727&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,067</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room Mate Collection Filippo, Rome-Fontana di Trevi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/room-mate-filippo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=91&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=585430201_229113126_0_1_0_303444&amp;highlighted_blocks=585430201_229113126_0_1_0_303444&amp;matching_block_id=585430201_229113126_0_1_0_303444&amp;sr_pri_blocks=585430201_229113126_0_1_0_303444_147729&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,477</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Stendhal Luxury Suites</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/stendhal-dependance-luxury-suite.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=92&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=124991942_0_2_1_0&amp;highlighted_blocks=124991942_0_2_1_0&amp;matching_block_id=124991942_0_2_1_0&amp;sr_pri_blocks=124991942_0_2_1_0__95448&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 954</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Executive Double or Twin Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alpi Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/alpi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=93&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=8306909_0_2_0_0&amp;highlighted_blocks=8306909_0_2_0_0&amp;matching_block_id=8306909_0_2_0_0&amp;sr_pri_blocks=8306909_0_2_0_0__78504&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 785</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Santa Prassede</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/santa-prassede.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=94&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=4867102_88152754_2_0_0&amp;highlighted_blocks=4867102_88152754_2_0_0&amp;matching_block_id=4867102_88152754_2_0_0&amp;sr_pri_blocks=4867102_88152754_2_0_0__72200&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 722</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH Collection Roma Giustiniano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/nh-collection-roma-giustiniano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=95&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=0_0_2_0_0&amp;highlighted_blocks=0_0_2_0_0&amp;matching_block_id=0_0_2_0_0&amp;sr_pri_blocks=0_0_2_0_0__106443&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,064</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Premier room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Milani</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/milani.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=96&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=8200507_123857379_2_1_0&amp;highlighted_blocks=8200507_123857379_2_1_0&amp;matching_block_id=8200507_123857379_2_1_0&amp;sr_pri_blocks=8200507_123857379_2_1_0__69630&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 696</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Condotti Boutique Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/condotti.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=97&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=8926823_415408888_0_2_0&amp;highlighted_blocks=8926823_415408888_0_2_0&amp;matching_block_id=8926823_415408888_0_2_0&amp;sr_pri_blocks=8926823_415408888_0_2_0__123630&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,236</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standard Double Room - Via del Corso 81</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The Spotlight Boutique Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/the-spotlight-boutique.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=98&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=1469612501_0_2_0_0&amp;highlighted_blocks=1469612501_0_2_0_0&amp;matching_block_id=1469612501_0_2_0_0&amp;sr_pri_blocks=1469612501_0_2_0_0__111524&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,115</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gioberti Art Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/gioberti-art.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=99&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026358&amp;all_sr_blocks=154108401_0_2_1_0&amp;highlighted_blocks=154108401_0_2_1_0&amp;matching_block_id=154108401_0_2_1_0&amp;sr_pri_blocks=154108401_0_2_1_0__79152&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 792</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Lirico</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotellirico.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=100&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=8189604_0_2_0_0&amp;highlighted_blocks=8189604_0_2_0_0&amp;matching_block_id=8189604_0_2_0_0&amp;sr_pri_blocks=8189604_0_2_0_0__79290&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 793</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Hiberia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hiberiahotelrome.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=101&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=8058402_88153650_0_1_0&amp;highlighted_blocks=8058402_88153650_0_1_0&amp;matching_block_id=8058402_88153650_0_1_0&amp;sr_pri_blocks=8058402_88153650_0_1_0__97403&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 974</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEININGER Roma Termini</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/meininger-roma-termini.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=102&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=269585803_106030219_0_2_0_496234&amp;highlighted_blocks=269585803_106030219_0_2_0_496234&amp;matching_block_id=269585803_106030219_0_2_0_496234&amp;sr_pri_blocks=269585803_106030219_0_2_0_496234_58125&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 581</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The Hive Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/the-hive.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=103&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=347454201_0_2_0_0&amp;highlighted_blocks=347454201_0_2_0_0&amp;matching_block_id=347454201_0_2_0_0&amp;sr_pri_blocks=347454201_0_2_0_0__91550&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 916</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Texas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hoteltexasroma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=104&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=8093804_410475774_0_0_0&amp;highlighted_blocks=8093804_410475774_0_0_0&amp;matching_block_id=8093804_410475774_0_0_0&amp;sr_pri_blocks=8093804_410475774_0_0_0__36000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 360</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Twin Room with Shared Bathroom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mercure Roma Piazza Bologna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/mercure-roma-piazza-bologna.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=105&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=8525507_94299175_2_2_0&amp;highlighted_blocks=8525507_94299175_2_2_0&amp;matching_block_id=8525507_94299175_2_2_0&amp;sr_pri_blocks=8525507_94299175_2_2_0__69724&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 697</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NYX Hotel Rome by Leonardo Hotels</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/cicerone.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=106&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=8414342_91462482_0_2_0&amp;highlighted_blocks=8414342_91462482_0_2_0&amp;matching_block_id=8414342_91462482_0_2_0&amp;sr_pri_blocks=8414342_91462482_0_2_0__104250&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Down to Earth Twin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Museum</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/alimandi-via-tunisi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=107&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=8361902_0_2_0_0&amp;highlighted_blocks=8361902_0_2_0_0&amp;matching_block_id=8361902_0_2_0_0&amp;sr_pri_blocks=8361902_0_2_0_0__47757&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 478</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Noba Hotel e Residenze</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/art-noba.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=108&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=23988516_88443741_2_2_0_417411&amp;highlighted_blocks=23988516_88443741_2_2_0_417411&amp;matching_block_id=23988516_88443741_2_2_0_417411&amp;sr_pri_blocks=23988516_88443741_2_2_0_417411_48257&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H10 Roma Città</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/h10-roma-citta.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=109&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=1856402_95143433_0_2_0_225253&amp;highlighted_blocks=1856402_95143433_0_2_0_225253&amp;matching_block_id=1856402_95143433_0_2_0_225253&amp;sr_pri_blocks=1856402_95143433_0_2_0_225253_48279&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOTEL DELLE CIVETTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/delle-civette.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=110&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=1120809905_0_2_1_0&amp;highlighted_blocks=1120809905_0_2_1_0&amp;matching_block_id=1120809905_0_2_1_0&amp;sr_pri_blocks=1120809905_0_2_1_0__57955&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 580</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Scenario</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/scenario.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=111&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=547338601_197738288_2_2_0&amp;highlighted_blocks=547338601_197738288_2_2_0&amp;matching_block_id=547338601_197738288_2_2_0&amp;sr_pri_blocks=547338601_197738288_2_2_0__126521&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,265</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Mercure Roma Corso Trieste</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/mercure-corso-trieste.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=112&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=8547008_94299409_2_42_0&amp;highlighted_blocks=8547008_94299409_2_42_0&amp;matching_block_id=8547008_94299409_2_42_0&amp;sr_pri_blocks=8547008_94299409_2_42_0__60800&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 608</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Parioli Cube Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/parioli-cube.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=113&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=1352601206_407587930_2_2_0&amp;highlighted_blocks=1352601206_407587930_2_2_0&amp;matching_block_id=1352601206_407587930_2_2_0&amp;sr_pri_blocks=1352601206_407587930_2_2_0__101668&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Suite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Livia Valeria Palace</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/livia-valeria-palace-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=114&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=762251004_426786985_2_1_0&amp;highlighted_blocks=762251004_426786985_2_1_0&amp;matching_block_id=762251004_426786985_2_1_0&amp;sr_pri_blocks=762251004_426786985_2_1_0__72960&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 730</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ludovisi Palace Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/ludovisipalacehotelroma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=115&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=8101602_0_2_1_0&amp;highlighted_blocks=8101602_0_2_1_0&amp;matching_block_id=8101602_0_2_1_0&amp;sr_pri_blocks=8101602_0_2_1_0__79566&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Mozart</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/mozart.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=116&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=1245323_95135887_0_2_0&amp;highlighted_blocks=1245323_95135887_0_2_0&amp;matching_block_id=1245323_95135887_0_2_0&amp;sr_pri_blocks=1245323_95135887_0_2_0__91650&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 917</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Double or Twin Room - Annex Building - Via del Corso 75</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mercure Roma Cinecittà</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/movie-movie.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=117&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=622381010_242541323_2_2_0&amp;highlighted_blocks=622381010_242541323_2_2_0&amp;matching_block_id=622381010_242541323_2_2_0&amp;sr_pri_blocks=622381010_242541323_2_2_0__50501&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Classic Twin Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BB Hotels Smarthotel Bailey's</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/baileyshotel.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=118&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=8050305_362128622_2_0_0&amp;highlighted_blocks=8050305_362128622_2_0_0&amp;matching_block_id=8050305_362128622_2_0_0&amp;sr_pri_blocks=8050305_362128622_2_0_0__80000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 800</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Small Double Classic Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Regina Margherita</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/regina-margherita.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=119&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=27979801_88165200_0_0_0&amp;highlighted_blocks=27979801_88165200_0_0_0&amp;matching_block_id=27979801_88165200_0_0_0&amp;sr_pri_blocks=27979801_88165200_0_0_0__58286&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 583</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LH Hotel Andreotti</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/andreotti.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=120&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=1466907_0_2_0_0&amp;highlighted_blocks=1466907_0_2_0_0&amp;matching_block_id=1466907_0_2_0_0&amp;sr_pri_blocks=1466907_0_2_0_0__53033&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 530</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Terrace Pantheon Relais</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/la-maison-d-39-art-luxury-suite.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=121&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=127593403_0_2_1_0&amp;highlighted_blocks=127593403_0_2_1_0&amp;matching_block_id=127593403_0_2_1_0&amp;sr_pri_blocks=127593403_0_2_1_0__144986&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,450</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Leonardo Boutique Hotel Rome Monti</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/dei-borgia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=122&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=55834735_88466378_0_2_0&amp;highlighted_blocks=55834735_88466378_0_2_0&amp;matching_block_id=55834735_88466378_0_2_0&amp;sr_pri_blocks=55834735_88466378_0_2_0__123240&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,232</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comfort Double Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Best Western Cinemusic Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/cinemusic.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=123&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=8947409_88441012_2_2_0&amp;highlighted_blocks=8947409_88441012_2_2_0&amp;matching_block_id=8947409_88441012_2_2_0&amp;sr_pri_blocks=8947409_88441012_2_2_0__69508&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 695</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Deluxe Queen Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Mecenate Palace</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/gtmecenate.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=124&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026370&amp;all_sr_blocks=8021302_0_2_0_0&amp;highlighted_blocks=8021302_0_2_0_0&amp;matching_block_id=8021302_0_2_0_0&amp;sr_pri_blocks=8021302_0_2_0_0__68853&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 689</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kolbe Hotel Rome</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/kolbe-rome.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=125&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=8935501_0_2_1_0&amp;highlighted_blocks=8935501_0_2_1_0&amp;matching_block_id=8935501_0_2_1_0&amp;sr_pri_blocks=8935501_0_2_1_0__109341&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Homs</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/homs.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=126&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=0_0_2_0_0&amp;highlighted_blocks=0_0_2_0_0&amp;matching_block_id=0_0_2_0_0&amp;sr_pri_blocks=0_0_2_0_0__61682&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 617</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Radisson Blu GHR Rome</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/grand-ritz.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=127&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=8414139_88158040_2_42_0&amp;highlighted_blocks=8414139_88158040_2_42_0&amp;matching_block_id=8414139_88158040_2_42_0&amp;sr_pri_blocks=8414139_88158040_2_42_0__89100&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 891</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standard Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Albergo Ottocento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/albergo-ottocento.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=128&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=8531902_91907617_0_1_0_709926&amp;highlighted_blocks=8531902_91907617_0_1_0_709926&amp;matching_block_id=8531902_91907617_0_1_0_709926&amp;sr_pri_blocks=8531902_91907617_0_1_0_709926_108415&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,084</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Cilicia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/cilicia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=129&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=24199802_88163140_2_1_0&amp;highlighted_blocks=24199802_88163140_2_1_0&amp;matching_block_id=24199802_88163140_2_1_0&amp;sr_pri_blocks=24199802_88163140_2_1_0__42396&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 424</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Euro Quiris</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hoteleuroquiris.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=130&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=8181903_362888097_0_0_0&amp;highlighted_blocks=8181903_362888097_0_0_0&amp;matching_block_id=8181903_362888097_0_0_0&amp;sr_pri_blocks=8181903_362888097_0_0_0__38500&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 385</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Basilica Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/domus-nova-bethlem.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=131&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=163792101_91456013_2_2_0_870314&amp;highlighted_blocks=163792101_91456013_2_2_0_870314&amp;matching_block_id=163792101_91456013_2_2_0_870314&amp;sr_pri_blocks=163792101_91456013_2_2_0_870314_86511&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 865</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hilton Rome Eur La Lama</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hilton-rome-eur-convention-center-italy.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=132&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=581141106_226081788_2_42_0&amp;highlighted_blocks=581141106_226081788_2_42_0&amp;matching_block_id=581141106_226081788_2_42_0&amp;sr_pri_blocks=581141106_226081788_2_42_0__120975&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>King Guest Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Fellini a Fontana di Trevi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/fellini-inn-rome.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=133&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=8815008_88160426_0_2_0&amp;highlighted_blocks=8815008_88160426_0_2_0&amp;matching_block_id=8815008_88160426_0_2_0&amp;sr_pri_blocks=8815008_88160426_0_2_0__78406&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 784</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lungotevere Suite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/lungotevere-suite.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=134&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=27555807_0_2_0_0&amp;highlighted_blocks=27555807_0_2_0_0&amp;matching_block_id=27555807_0_2_0_0&amp;sr_pri_blocks=27555807_0_2_0_0__45278&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 453</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Classic Double Room with Balcony</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vibe Nazionale</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/vibe-giolli-nazionale.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=135&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=129274160_87942100_0_34_0_1132516&amp;highlighted_blocks=129274160_87942100_0_34_0_1132516&amp;matching_block_id=129274160_87942100_0_34_0_1132516&amp;sr_pri_blocks=129274160_87942100_0_34_0_1132516_89820&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 898</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Albergo Abruzzi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/albergo-abruzzi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=136&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=8825502_0_2_1_0&amp;highlighted_blocks=8825502_0_2_1_0&amp;matching_block_id=8825502_0_2_1_0&amp;sr_pri_blocks=8825502_0_2_1_0__112756&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,128</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Double or Twin Room with Pantheon View</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Meridiana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/meridianaroma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=137&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=0_0_2_0_0&amp;highlighted_blocks=0_0_2_0_0&amp;matching_block_id=0_0_2_0_0&amp;sr_pri_blocks=0_0_2_0_0__33599&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 336</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Double Bed room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hilton Garden Inn Rome Claridge</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotel-claridge-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=138&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=8414010_94298463_2_34_0_927271&amp;highlighted_blocks=8414010_94298463_2_34_0_927271&amp;matching_block_id=8414010_94298463_2_34_0_927271&amp;sr_pri_blocks=8414010_94298463_2_34_0_927271_70796&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 708</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Twin Room - Mobility Access</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Marc'Aurelio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/marc-aurelio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=139&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=1369201_95137967_2_1_0&amp;highlighted_blocks=1369201_95137967_2_1_0&amp;matching_block_id=1369201_95137967_2_1_0&amp;sr_pri_blocks=1369201_95137967_2_1_0__55545&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Concordia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotelconcordiaroma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=140&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=8106201_88435157_2_2_0&amp;highlighted_blocks=8106201_88435157_2_2_0&amp;matching_block_id=8106201_88435157_2_2_0&amp;sr_pri_blocks=8106201_88435157_2_2_0__85592&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 856</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TB Place Roma</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/tb-place.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=141&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=1029654004_0_2_1_0&amp;highlighted_blocks=1029654004_0_2_1_0&amp;matching_block_id=1029654004_0_2_1_0&amp;sr_pri_blocks=1029654004_0_2_1_0__199461&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,995</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Silva</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotelsilva.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=142&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=8024034_88153089_2_2_0&amp;highlighted_blocks=8024034_88153089_2_2_0&amp;matching_block_id=8024034_88153089_2_2_0&amp;sr_pri_blocks=8024034_88153089_2_2_0__50791&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 508</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Economy Double or Twin Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Euromoon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/euromoon.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=143&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=1481761401_419671385_2_0_0&amp;highlighted_blocks=1481761401_419671385_2_0_0&amp;matching_block_id=1481761401_419671385_2_0_0&amp;sr_pri_blocks=1481761401_419671385_2_0_0__29030&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 290</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Lunetta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/lunetta.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=144&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=31804501_0_2_1_0&amp;highlighted_blocks=31804501_0_2_1_0&amp;matching_block_id=31804501_0_2_1_0&amp;sr_pri_blocks=31804501_0_2_1_0__183142&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,831</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Best Western Premier Hotel Royal Santina</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotel-royal-santina.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=145&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=8413913_88920344_2_42_0&amp;highlighted_blocks=8413913_88920344_2_42_0&amp;matching_block_id=8413913_88920344_2_42_0&amp;sr_pri_blocks=8413913_88920344_2_42_0__110955&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,110</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comfort King Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Ripa Roma</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/gtripa.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=146&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=8020802_0_2_1_0&amp;highlighted_blocks=8020802_0_2_1_0&amp;matching_block_id=8020802_0_2_1_0&amp;sr_pri_blocks=8020802_0_2_1_0__67614&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 676</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standard Double Room with Balcony</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Mariano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/mariano-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=147&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=8427626_207743514_2_0_0&amp;highlighted_blocks=8427626_207743514_2_0_0&amp;matching_block_id=8427626_207743514_2_0_0&amp;sr_pri_blocks=8427626_207743514_2_0_0__54436&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 544</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Canada, BW Premier Collection</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/best-western-canada.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=148&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=90812238_0_2_0_0&amp;highlighted_blocks=90812238_0_2_0_0&amp;matching_block_id=90812238_0_2_0_0&amp;sr_pri_blocks=90812238_0_2_0_0__83156&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 832</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comfort Twin Room - Non-Smoking</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47 Boutique Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/fortyseven.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=149&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026380&amp;all_sr_blocks=4887102_0_2_1_0&amp;highlighted_blocks=4887102_0_2_1_0&amp;matching_block_id=4887102_0_2_1_0&amp;sr_pri_blocks=4887102_0_2_1_0__111454&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Roma Tiburtina Metro</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/tibur-metro-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=150&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=30589406_0_2_1_0&amp;highlighted_blocks=30589406_0_2_1_0&amp;matching_block_id=30589406_0_2_1_0&amp;sr_pri_blocks=30589406_0_2_1_0__42740&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 427</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Tito</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/tito-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=151&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=202750104_0_2_0_0&amp;highlighted_blocks=202750104_0_2_0_0&amp;matching_block_id=202750104_0_2_0_0&amp;sr_pri_blocks=202750104_0_2_0_0__64117&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 641</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Caravaggio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/caravaggio-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=152&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=19075102_88162357_0_2_0&amp;highlighted_blocks=19075102_88162357_0_2_0&amp;matching_block_id=19075102_88162357_0_2_0&amp;sr_pri_blocks=19075102_88162357_0_2_0__64417&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 644</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The Sanctuary Urban Retreat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/the-sanctuary-urban-retreat.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=153&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=987480801_0_2_0_0&amp;highlighted_blocks=987480801_0_2_0_0&amp;matching_block_id=987480801_0_2_0_0&amp;sr_pri_blocks=987480801_0_2_0_0__90766&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 908</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room Mate Collection Gran Filippo, Rome-Fontana di Trevi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/room-mate-gran-filippo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=154&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=587487101_230373758_2_0_0_303446&amp;highlighted_blocks=587487101_230373758_2_0_0_303446&amp;matching_block_id=587487101_230373758_2_0_0_303446&amp;sr_pri_blocks=587487101_230373758_2_0_0_303446_137416&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,374</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Villa Angelina</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/checkin-villa-angelica.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=155&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=273414715_106378190_0_1_0&amp;highlighted_blocks=273414715_106378190_0_1_0&amp;matching_block_id=273414715_106378190_0_1_0&amp;sr_pri_blocks=273414715_106378190_0_1_0__64821&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 648</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Palazzo Ripetta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/residenza-di-ripetta.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=156&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=18659268_0_2_0_0&amp;highlighted_blocks=18659268_0_2_0_0&amp;matching_block_id=18659268_0_2_0_0&amp;sr_pri_blocks=18659268_0_2_0_0__209822&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 2,098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Occidental Aurelia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/esh-executive-style.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=157&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=0_0_2_0_0&amp;highlighted_blocks=0_0_2_0_0&amp;matching_block_id=0_0_2_0_0&amp;sr_pri_blocks=0_0_2_0_0__39600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 396</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Double or Twin Superior</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ibis Styles Roma Eur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/mm.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=158&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=43993912_94466284_2_2_0&amp;highlighted_blocks=43993912_94466284_2_2_0&amp;matching_block_id=43993912_94466284_2_2_0&amp;sr_pri_blocks=43993912_94466284_2_2_0__59585&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 596</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Superior Twin Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Diplomatic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/diplomaticroma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=159&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=8121502_0_2_1_0&amp;highlighted_blocks=8121502_0_2_1_0&amp;matching_block_id=8121502_0_2_1_0&amp;sr_pri_blocks=8121502_0_2_1_0__77003&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 770</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grand Hotel Tiberio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/grand-tiberio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=160&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=8314002_207987275_2_1_0&amp;highlighted_blocks=8314002_207987275_2_1_0&amp;matching_block_id=8314002_207987275_2_1_0&amp;sr_pri_blocks=8314002_207987275_2_1_0__66395&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 664</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Old Town Home Trastevere</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/horti-14-home.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=161&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=596943101_234037772_0_2_0&amp;highlighted_blocks=596943101_234037772_0_2_0&amp;matching_block_id=596943101_234037772_0_2_0&amp;sr_pri_blocks=596943101_234037772_0_2_0__64706&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 647</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Borromeo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/borromeo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=162&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=8053902_88919711_2_1_0&amp;highlighted_blocks=8053902_88919711_2_1_0&amp;matching_block_id=8053902_88919711_2_1_0&amp;sr_pri_blocks=8053902_88919711_2_1_0__110844&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,108</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel American Palace Eur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/american-palace-eur.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=163&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=4470602_93697888_2_1_0&amp;highlighted_blocks=4470602_93697888_2_1_0&amp;matching_block_id=4470602_93697888_2_1_0&amp;sr_pri_blocks=4470602_93697888_2_1_0__87000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 870</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Martis Palace</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/martis-palace.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=164&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=170737302_370897098_0_1_0&amp;highlighted_blocks=170737302_370897098_0_1_0&amp;matching_block_id=170737302_370897098_0_1_0&amp;sr_pri_blocks=170737302_370897098_0_1_0__229000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 2,290</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Robinson</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/robinson.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=165&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=30903103_424689315_2_0_0&amp;highlighted_blocks=30903103_424689315_2_0_0&amp;matching_block_id=30903103_424689315_2_0_0&amp;sr_pri_blocks=30903103_424689315_2_0_0__45140&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 451</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Trame</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/trame.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=166&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=1495478701_421220286_2_0_0&amp;highlighted_blocks=1495478701_421220286_2_0_0&amp;matching_block_id=1495478701_421220286_2_0_0&amp;sr_pri_blocks=1495478701_421220286_2_0_0__138193&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,382</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Splendide Royal - The Leading Hotels of the World</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/splendide-royal.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=167&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=0_0_2_0_0&amp;highlighted_blocks=0_0_2_0_0&amp;matching_block_id=0_0_2_0_0&amp;sr_pri_blocks=0_0_2_0_0__203685&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 2,037</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Partner offer option</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Royal Court</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/royalcourtroma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=168&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=0_0_2_0_0&amp;highlighted_blocks=0_0_2_0_0&amp;matching_block_id=0_0_2_0_0&amp;sr_pri_blocks=0_0_2_0_0__71700&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 717</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standard Double Room - Dependence</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grand Hotel Plaza</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/plaza.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=169&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=8004501_0_2_0_0&amp;highlighted_blocks=8004501_0_2_0_0&amp;matching_block_id=8004501_0_2_0_0&amp;sr_pri_blocks=8004501_0_2_0_0__167844&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,678</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Diocleziano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/diocleziano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=170&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=8450701_88158182_2_2_0&amp;highlighted_blocks=8450701_88158182_2_2_0&amp;matching_block_id=8450701_88158182_2_2_0&amp;sr_pri_blocks=8450701_88158182_2_2_0__78724&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 787</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Relais Fontana Di Trevi Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/relais-fontana-di-trevi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=171&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=0_0_2_0_0&amp;highlighted_blocks=0_0_2_0_0&amp;matching_block_id=0_0_2_0_0&amp;sr_pri_blocks=0_0_2_0_0__91708&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hearth Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hearth.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=172&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=49676008_383080704_0_0_0&amp;highlighted_blocks=49676008_383080704_0_0_0&amp;matching_block_id=49676008_383080704_0_0_0&amp;sr_pri_blocks=49676008_383080704_0_0_0__68038&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 680</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Torre Capranica</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/torre-capranica.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=173&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=928391304_368467694_2_0_0&amp;highlighted_blocks=928391304_368467694_2_0_0&amp;matching_block_id=928391304_368467694_2_0_0&amp;sr_pri_blocks=928391304_368467694_2_0_0__112445&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,124</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Suite with City View</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trilussa Palace Hotel Congress &amp; Spa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/trilussa-palace.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=174&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026391&amp;all_sr_blocks=8337619_88157507_2_2_0&amp;highlighted_blocks=8337619_88157507_2_2_0&amp;matching_block_id=8337619_88157507_2_2_0&amp;sr_pri_blocks=8337619_88157507_2_2_0__112201&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,122</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Best Western Plus Hotel Universo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/best-western-plus-universo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=175&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=8413114_0_2_0_0&amp;highlighted_blocks=8413114_0_2_0_0&amp;matching_block_id=8413114_0_2_0_0&amp;sr_pri_blocks=8413114_0_2_0_0__90099&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 901</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Paolo II</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/paolo-ii.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=176&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=196374011_0_2_0_0&amp;highlighted_blocks=196374011_0_2_0_0&amp;matching_block_id=196374011_0_2_0_0&amp;sr_pri_blocks=196374011_0_2_0_0__57818&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 578</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Best Western Hotel Astrid</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/astridhotel.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=177&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=8299612_0_2_0_0&amp;highlighted_blocks=8299612_0_2_0_0&amp;matching_block_id=8299612_0_2_0_0&amp;sr_pri_blocks=8299612_0_2_0_0__62497&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comfort Queen Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Palazzo Nainer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/palazzonainer.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=178&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=8868216_88440422_2_2_0&amp;highlighted_blocks=8868216_88440422_2_2_0&amp;matching_block_id=8868216_88440422_2_2_0&amp;sr_pri_blocks=8868216_88440422_2_2_0__193218&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Deluxe King Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mercure Roma Centro Colosseo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/mercure-delta-colosseo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=179&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=8546916_94299355_2_2_0&amp;highlighted_blocks=8546916_94299355_2_2_0&amp;matching_block_id=8546916_94299355_2_2_0&amp;sr_pri_blocks=8546916_94299355_2_2_0__124320&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,243</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Reyes Suite &amp; Rooms</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/reyes-suite.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=180&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=1173739409_389947011_0_0_0&amp;highlighted_blocks=1173739409_389947011_0_0_0&amp;matching_block_id=1173739409_389947011_0_0_0&amp;sr_pri_blocks=1173739409_389947011_0_0_0__34500&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 345</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Navona Street Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/navona-street.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=181&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=209837303_95814784_2_41_0&amp;highlighted_blocks=209837303_95814784_2_41_0&amp;matching_block_id=209837303_95814784_2_41_0&amp;sr_pri_blocks=209837303_95814784_2_41_0__123655&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,237</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Patrizia Romana Palace</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/patrizia-romana-palace.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=182&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=25929501_388266541_2_0_0&amp;highlighted_blocks=25929501_388266541_2_0_0&amp;matching_block_id=25929501_388266541_2_0_0&amp;sr_pri_blocks=25929501_388266541_2_0_0__61341&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 613</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Classic Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Franklin Feel The Sound</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotel-franklin-feel-the-sound.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=183&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=8030703_88919636_0_2_0&amp;highlighted_blocks=8030703_88919636_0_2_0&amp;matching_block_id=8030703_88919636_0_2_0&amp;sr_pri_blocks=8030703_88919636_0_2_0__51701&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 517</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Monte Verde</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/monte-verde-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=184&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=1146372806_387462360_2_1_0&amp;highlighted_blocks=1146372806_387462360_2_1_0&amp;matching_block_id=1146372806_387462360_2_1_0&amp;sr_pri_blocks=1146372806_387462360_2_1_0__46440&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 464</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Relais Dei Papi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/relais-dei-papi-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=185&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=33326602_0_2_0_0&amp;highlighted_blocks=33326602_0_2_0_0&amp;matching_block_id=33326602_0_2_0_0&amp;sr_pri_blocks=33326602_0_2_0_0__96578&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Villafranca</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/best-western-villafranca.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=186&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=0_0_2_1_0&amp;highlighted_blocks=0_0_2_1_0&amp;matching_block_id=0_0_2_1_0&amp;sr_pri_blocks=0_0_2_1_0__63115&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 631</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Superior Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rose Garden Palace Roma by OMNIA hotels</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/rose-garden-palace.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=187&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=1381419_113090310_2_0_0&amp;highlighted_blocks=1381419_113090310_2_0_0&amp;matching_block_id=1381419_113090310_2_0_0&amp;sr_pri_blocks=1381419_113090310_2_0_0__113378&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Relais Orso</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/relais-dell-orso.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=188&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=36153802_88055587_0_0_0&amp;highlighted_blocks=36153802_88055587_0_0_0&amp;matching_block_id=36153802_88055587_0_0_0&amp;sr_pri_blocks=36153802_88055587_0_0_0__140013&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,400</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Deluxe Double Room with Spa Bath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Barberini</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotelbarberiniroma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=189&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=0_0_2_0_0&amp;highlighted_blocks=0_0_2_0_0&amp;matching_block_id=0_0_2_0_0&amp;sr_pri_blocks=0_0_2_0_0__90973&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 910</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Numa Rome Linea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/numa-rome-linea.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=190&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=47159809_88464446_2_2_0_1190369&amp;highlighted_blocks=47159809_88464446_2_2_0_1190369&amp;matching_block_id=47159809_88464446_2_2_0_1190369&amp;sr_pri_blocks=47159809_88464446_2_2_0_1190369_69850&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 699</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Medium Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Al SanPietrino</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/al-sanpietrino.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=191&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=33265502_88171521_0_0_0&amp;highlighted_blocks=33265502_88171521_0_0_0&amp;matching_block_id=33265502_88171521_0_0_0&amp;sr_pri_blocks=33265502_88171521_0_0_0__50000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Esposizione Palace Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/esposizione-palace.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=192&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=248706009_103261991_2_0_0_251504&amp;highlighted_blocks=248706009_103261991_2_0_0_251504&amp;matching_block_id=248706009_103261991_2_0_0_251504&amp;sr_pri_blocks=248706009_103261991_2_0_0_251504_103847&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,038</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Laurentia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/laurentia-roma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=193&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=23890501_387804593_0_1_0&amp;highlighted_blocks=23890501_387804593_0_1_0&amp;matching_block_id=23890501_387804593_0_1_0&amp;sr_pri_blocks=23890501_387804593_0_1_0__70260&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 703</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vivaldi Luxury Rooms</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/vivaldi-luxury-rooms.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=194&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=31262201_413570527_0_2_0&amp;highlighted_blocks=31262201_413570527_0_2_0&amp;matching_block_id=31262201_413570527_0_2_0&amp;sr_pri_blocks=31262201_413570527_0_2_0__85475&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 855</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ateneo Garden Palace</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/ateneo-garden-palace.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=195&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=23890901_0_2_1_0&amp;highlighted_blocks=23890901_0_2_1_0&amp;matching_block_id=23890901_0_2_1_0&amp;sr_pri_blocks=23890901_0_2_1_0__73554&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 736</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel De Petris</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/de-petris.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=196&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=0_0_2_0_0&amp;highlighted_blocks=0_0_2_0_0&amp;matching_block_id=0_0_2_0_0&amp;sr_pri_blocks=0_0_2_0_0__70574&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 706</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Double or Twin Classic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Principe Eugenio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/principe-eugenio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=197&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=23648101_0_2_0_0&amp;highlighted_blocks=23648101_0_2_0_0&amp;matching_block_id=23648101_0_2_0_0&amp;sr_pri_blocks=23648101_0_2_0_0__55324&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 553</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Residenza Piranesi Boutique Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/residenza-piranesi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=198&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=1092884602_0_2_0_0&amp;highlighted_blocks=1092884602_0_2_0_0&amp;matching_block_id=1092884602_0_2_0_0&amp;sr_pri_blocks=1092884602_0_2_0_0__133996&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Nord Nuova Roma</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotelnordroma.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=199&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=0_0_2_1_0&amp;highlighted_blocks=0_0_2_1_0&amp;matching_block_id=0_0_2_1_0&amp;sr_pri_blocks=0_0_2_1_0__77601&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room Selected at Check-In</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nomos Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/nomos.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKf5sTLBsACAdICJDQ2MzA1ZmI5LTEyY2YtNGM2Yy04M2Q5LWJmNzFlNDdmZWRmONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-02-10&amp;checkout=2026-02-15&amp;dest_id=-126693&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=26&amp;hapos=200&amp;sr_order=popularity&amp;nflt=ht_id%3D204&amp;srpvid=2b228e1496570102&amp;srepoch=1769026403&amp;all_sr_blocks=1412269901_412970021_2_2_0&amp;highlighted_blocks=1412269901_412970021_2_2_0&amp;matching_block_id=1412269901_412970021_2_2_0&amp;sr_pri_blocks=1412269901_412970021_2_2_0__135564&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>€ 1,356</x:t>
+  </x:si>
+  <x:si>
     <x:t>AvgTemperature</x:t>
   </x:si>
   <x:si>
@@ -65,6 +2137,15 @@
     <x:t>WeatherDescription</x:t>
   </x:si>
   <x:si>
+    <x:t>-3.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The forecast for Roma during 10 February 2026 - 15 February 2026 shows an average temperature of -3.3°C with a rain probability of 33%.</x:t>
+  </x:si>
+  <x:si>
     <x:t>DepartureCity</x:t>
   </x:si>
   <x:si>
@@ -104,85 +2185,25 @@
     <x:t>Score</x:t>
   </x:si>
   <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Bucuresti</x:t>
   </x:si>
   <x:si>
     <x:t>Roma</x:t>
   </x:si>
   <x:si>
-    <x:t>10.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.06.2026</x:t>
+    <x:t>10.02.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.02.2026</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cluj</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Viena</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.07.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.07.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Iasi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Brasov</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Timisoara</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Paris</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RowIndex</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ErrorMessage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DepartureDate in the past; ReturnDate in the past; ReturnDate before DepartureDate; </x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DepartureCity missing; Passengers invalid; TotalBudget invalid; DepartureDate in the past; ReturnDate in the past; TransportPreference invalid; </x:t>
+    <x:t>Mixed weather</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Insufficient data</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -562,6 +2583,32 @@
         <x:v>7</x:v>
       </x:c>
     </x:row>
+    <x:row r="2" spans="1:8">
+      <x:c r="A2" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -584,19 +2631,3419 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E1" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F1" s="0" t="s">
         <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:6">
+      <x:c r="A2" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:6">
+      <x:c r="A3" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:6">
+      <x:c r="A4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:6">
+      <x:c r="A5" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:6">
+      <x:c r="A6" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:6">
+      <x:c r="A7" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:6">
+      <x:c r="A8" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:6">
+      <x:c r="A9" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:6">
+      <x:c r="A10" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:6">
+      <x:c r="A11" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:6">
+      <x:c r="A12" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:6">
+      <x:c r="A13" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:6">
+      <x:c r="A14" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:6">
+      <x:c r="A15" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:6">
+      <x:c r="A16" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:6">
+      <x:c r="A17" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:6">
+      <x:c r="A18" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:6">
+      <x:c r="A19" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:6">
+      <x:c r="A20" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:6">
+      <x:c r="A21" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:6">
+      <x:c r="A22" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:6">
+      <x:c r="A23" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:6">
+      <x:c r="A24" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:6">
+      <x:c r="A25" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:6">
+      <x:c r="A26" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:6">
+      <x:c r="A27" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:6">
+      <x:c r="A28" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:6">
+      <x:c r="A29" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:6">
+      <x:c r="A30" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:6">
+      <x:c r="A31" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:6">
+      <x:c r="A32" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="E32" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:6">
+      <x:c r="A33" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="E33" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:6">
+      <x:c r="A34" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="E34" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:6">
+      <x:c r="A35" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:6">
+      <x:c r="A36" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:6">
+      <x:c r="A37" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
+        <x:v>164</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:6">
+      <x:c r="A38" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E38" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:6">
+      <x:c r="A39" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:6">
+      <x:c r="A40" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="E40" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:6">
+      <x:c r="A41" s="0" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="E41" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:6">
+      <x:c r="A42" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="E42" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:6">
+      <x:c r="A43" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="E43" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:6">
+      <x:c r="A44" s="0" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="E44" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:6">
+      <x:c r="A45" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="E45" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:6">
+      <x:c r="A46" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="E46" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:6">
+      <x:c r="A47" s="0" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="E47" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:6">
+      <x:c r="A48" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="E48" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:6">
+      <x:c r="A49" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="E49" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:6">
+      <x:c r="A50" s="0" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="E50" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:6">
+      <x:c r="A51" s="0" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="E51" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:6">
+      <x:c r="A52" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D52" s="0" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="E52" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:6">
+      <x:c r="A53" s="0" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="E53" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:6">
+      <x:c r="A54" s="0" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="E54" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:6">
+      <x:c r="A55" s="0" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D55" s="0" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="E55" s="0" t="s">
+        <x:v>226</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:6">
+      <x:c r="A56" s="0" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="D56" s="0" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="E56" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:6">
+      <x:c r="A57" s="0" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="E57" s="0" t="s">
+        <x:v>234</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:6">
+      <x:c r="A58" s="0" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D58" s="0" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="E58" s="0" t="s">
+        <x:v>238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:6">
+      <x:c r="A59" s="0" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D59" s="0" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="E59" s="0" t="s">
+        <x:v>242</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:6">
+      <x:c r="A60" s="0" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="D60" s="0" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="E60" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:6">
+      <x:c r="A61" s="0" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D61" s="0" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="E61" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:6">
+      <x:c r="A62" s="0" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D62" s="0" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="E62" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:6">
+      <x:c r="A63" s="0" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D63" s="0" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="E63" s="0" t="s">
+        <x:v>164</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:6">
+      <x:c r="A64" s="0" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="C64" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D64" s="0" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="E64" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:6">
+      <x:c r="A65" s="0" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="C65" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D65" s="0" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="E65" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:6">
+      <x:c r="A66" s="0" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="C66" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D66" s="0" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="E66" s="0" t="s">
+        <x:v>264</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:6">
+      <x:c r="A67" s="0" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="C67" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D67" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="E67" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:6">
+      <x:c r="A68" s="0" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="C68" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D68" s="0" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="E68" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:6">
+      <x:c r="A69" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="D69" s="0" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="E69" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:6">
+      <x:c r="A70" s="0" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D70" s="0" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="E70" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:6">
+      <x:c r="A71" s="0" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="D71" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="E71" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:6">
+      <x:c r="A72" s="0" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="D72" s="0" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="E72" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:6">
+      <x:c r="A73" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D73" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="E73" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:6">
+      <x:c r="A74" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="C74" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D74" s="0" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="E74" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:6">
+      <x:c r="A75" s="0" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="C75" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D75" s="0" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="E75" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:6">
+      <x:c r="A76" s="0" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="B76" s="0" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="C76" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D76" s="0" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E76" s="0" t="s">
+        <x:v>296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:6">
+      <x:c r="A77" s="0" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="B77" s="0" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="C77" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D77" s="0" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="E77" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:6">
+      <x:c r="A78" s="0" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B78" s="0" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="C78" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D78" s="0" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="E78" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:6">
+      <x:c r="A79" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="C79" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="D79" s="0" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="E79" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:6">
+      <x:c r="A80" s="0" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="C80" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E80" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:6">
+      <x:c r="A81" s="0" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="C81" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D81" s="0" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="E81" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:6">
+      <x:c r="A82" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="C82" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D82" s="0" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="E82" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:6">
+      <x:c r="A83" s="0" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="C83" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D83" s="0" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="E83" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:6">
+      <x:c r="A84" s="0" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="C84" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D84" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="E84" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:6">
+      <x:c r="A85" s="0" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="C85" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="D85" s="0" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="E85" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:6">
+      <x:c r="A86" s="0" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="C86" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="D86" s="0" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="E86" s="0" t="s">
+        <x:v>326</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:6">
+      <x:c r="A87" s="0" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="C87" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D87" s="0" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="E87" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:6">
+      <x:c r="A88" s="0" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="C88" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D88" s="0" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="E88" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:6">
+      <x:c r="A89" s="0" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="C89" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D89" s="0" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="E89" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:6">
+      <x:c r="A90" s="0" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D90" s="0" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="E90" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:6">
+      <x:c r="A91" s="0" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="C91" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D91" s="0" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="E91" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:6">
+      <x:c r="A92" s="0" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="B92" s="0" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="C92" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D92" s="0" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="E92" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:6">
+      <x:c r="A93" s="0" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="B93" s="0" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="C93" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D93" s="0" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="E93" s="0" t="s">
+        <x:v>347</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:6">
+      <x:c r="A94" s="0" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="B94" s="0" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="C94" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D94" s="0" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="E94" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:6">
+      <x:c r="A95" s="0" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="B95" s="0" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="C95" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D95" s="0" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="E95" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:6">
+      <x:c r="A96" s="0" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="C96" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D96" s="0" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="E96" s="0" t="s">
+        <x:v>357</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:6">
+      <x:c r="A97" s="0" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D97" s="0" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="E97" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:6">
+      <x:c r="A98" s="0" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D98" s="0" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="E98" s="0" t="s">
+        <x:v>364</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:6">
+      <x:c r="A99" s="0" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="C99" s="0" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="D99" s="0" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="E99" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:6">
+      <x:c r="A100" s="0" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="B100" s="0" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="C100" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D100" s="0" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="E100" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:6">
+      <x:c r="A101" s="0" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D101" s="0" t="s">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="E101" s="0" t="s">
+        <x:v>238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:6">
+      <x:c r="A102" s="0" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="B102" s="0" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="C102" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D102" s="0" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="E102" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:6">
+      <x:c r="A103" s="0" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="B103" s="0" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="C103" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D103" s="0" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="E103" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:6">
+      <x:c r="A104" s="0" t="s">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="B104" s="0" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="C104" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D104" s="0" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="E104" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:6">
+      <x:c r="A105" s="0" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="B105" s="0" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="C105" s="0" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="D105" s="0" t="s">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="E105" s="0" t="s">
+        <x:v>388</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:6">
+      <x:c r="A106" s="0" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="B106" s="0" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="C106" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D106" s="0" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="E106" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:6">
+      <x:c r="A107" s="0" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="B107" s="0" t="s">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="C107" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D107" s="0" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="E107" s="0" t="s">
+        <x:v>395</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:6">
+      <x:c r="A108" s="0" t="s">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="B108" s="0" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="C108" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D108" s="0" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="E108" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:6">
+      <x:c r="A109" s="0" t="s">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="B109" s="0" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="C109" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D109" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="E109" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:6">
+      <x:c r="A110" s="0" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="B110" s="0" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="C110" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D110" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="E110" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:6">
+      <x:c r="A111" s="0" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="B111" s="0" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="C111" s="0" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="D111" s="0" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="E111" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:6">
+      <x:c r="A112" s="0" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="C112" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D112" s="0" t="s">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="E112" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:6">
+      <x:c r="A113" s="0" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="C113" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D113" s="0" t="s">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="E113" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:6">
+      <x:c r="A114" s="0" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="B114" s="0" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="C114" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D114" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="E114" s="0" t="s">
+        <x:v>415</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:6">
+      <x:c r="A115" s="0" t="s">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="C115" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D115" s="0" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="E115" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:6">
+      <x:c r="A116" s="0" t="s">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="C116" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D116" s="0" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="E116" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:6">
+      <x:c r="A117" s="0" t="s">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="C117" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D117" s="0" t="s">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="E117" s="0" t="s">
+        <x:v>424</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:6">
+      <x:c r="A118" s="0" t="s">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="B118" s="0" t="s">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="C118" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D118" s="0" t="s">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="E118" s="0" t="s">
+        <x:v>428</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:6">
+      <x:c r="A119" s="0" t="s">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="C119" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D119" s="0" t="s">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="E119" s="0" t="s">
+        <x:v>432</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:6">
+      <x:c r="A120" s="0" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="C120" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D120" s="0" t="s">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="E120" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:6">
+      <x:c r="A121" s="0" t="s">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="C121" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D121" s="0" t="s">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="E121" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:6">
+      <x:c r="A122" s="0" t="s">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="B122" s="0" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="C122" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="D122" s="0" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="E122" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:6">
+      <x:c r="A123" s="0" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="B123" s="0" t="s">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="C123" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D123" s="0" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="E123" s="0" t="s">
+        <x:v>445</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:6">
+      <x:c r="A124" s="0" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="C124" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D124" s="0" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="E124" s="0" t="s">
+        <x:v>449</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:6">
+      <x:c r="A125" s="0" t="s">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="B125" s="0" t="s">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="C125" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D125" s="0" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="E125" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:6">
+      <x:c r="A126" s="0" t="s">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="B126" s="0" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="C126" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D126" s="0" t="s">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="E126" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:6">
+      <x:c r="A127" s="0" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="C127" s="0" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D127" s="0" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="E127" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:6">
+      <x:c r="A128" s="0" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="C128" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D128" s="0" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="E128" s="0" t="s">
+        <x:v>462</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:6">
+      <x:c r="A129" s="0" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="B129" s="0" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="C129" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D129" s="0" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="E129" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:6">
+      <x:c r="A130" s="0" t="s">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="C130" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D130" s="0" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="E130" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:6">
+      <x:c r="A131" s="0" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="C131" s="0" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="D131" s="0" t="s">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="E131" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:6">
+      <x:c r="A132" s="0" t="s">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="C132" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D132" s="0" t="s">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="E132" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:6">
+      <x:c r="A133" s="0" t="s">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="B133" s="0" t="s">
+        <x:v>476</x:v>
+      </x:c>
+      <x:c r="C133" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D133" s="0" t="s">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="E133" s="0" t="s">
+        <x:v>478</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:6">
+      <x:c r="A134" s="0" t="s">
+        <x:v>479</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="C134" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D134" s="0" t="s">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="E134" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:6">
+      <x:c r="A135" s="0" t="s">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="C135" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D135" s="0" t="s">
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="E135" s="0" t="s">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:6">
+      <x:c r="A136" s="0" t="s">
+        <x:v>486</x:v>
+      </x:c>
+      <x:c r="B136" s="0" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="C136" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D136" s="0" t="s">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="E136" s="0" t="s">
+        <x:v>226</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:6">
+      <x:c r="A137" s="0" t="s">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="C137" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D137" s="0" t="s">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="E137" s="0" t="s">
+        <x:v>492</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" spans="1:6">
+      <x:c r="A138" s="0" t="s">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="B138" s="0" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="C138" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="D138" s="0" t="s">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="E138" s="0" t="s">
+        <x:v>496</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" spans="1:6">
+      <x:c r="A139" s="0" t="s">
+        <x:v>497</x:v>
+      </x:c>
+      <x:c r="B139" s="0" t="s">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="C139" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D139" s="0" t="s">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="E139" s="0" t="s">
+        <x:v>500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" spans="1:6">
+      <x:c r="A140" s="0" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="B140" s="0" t="s">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="C140" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D140" s="0" t="s">
+        <x:v>503</x:v>
+      </x:c>
+      <x:c r="E140" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" spans="1:6">
+      <x:c r="A141" s="0" t="s">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="B141" s="0" t="s">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="C141" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="D141" s="0" t="s">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="E141" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" spans="1:6">
+      <x:c r="A142" s="0" t="s">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="B142" s="0" t="s">
+        <x:v>508</x:v>
+      </x:c>
+      <x:c r="C142" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="D142" s="0" t="s">
+        <x:v>509</x:v>
+      </x:c>
+      <x:c r="E142" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" spans="1:6">
+      <x:c r="A143" s="0" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="B143" s="0" t="s">
+        <x:v>511</x:v>
+      </x:c>
+      <x:c r="C143" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D143" s="0" t="s">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="E143" s="0" t="s">
+        <x:v>513</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" spans="1:6">
+      <x:c r="A144" s="0" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="B144" s="0" t="s">
+        <x:v>515</x:v>
+      </x:c>
+      <x:c r="C144" s="0" t="s">
+        <x:v>516</x:v>
+      </x:c>
+      <x:c r="D144" s="0" t="s">
+        <x:v>517</x:v>
+      </x:c>
+      <x:c r="E144" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" spans="1:6">
+      <x:c r="A145" s="0" t="s">
+        <x:v>518</x:v>
+      </x:c>
+      <x:c r="B145" s="0" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="C145" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D145" s="0" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="E145" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" spans="1:6">
+      <x:c r="A146" s="0" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="B146" s="0" t="s">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="C146" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D146" s="0" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="E146" s="0" t="s">
+        <x:v>524</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" spans="1:6">
+      <x:c r="A147" s="0" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="B147" s="0" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="C147" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D147" s="0" t="s">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="E147" s="0" t="s">
+        <x:v>528</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" spans="1:6">
+      <x:c r="A148" s="0" t="s">
+        <x:v>529</x:v>
+      </x:c>
+      <x:c r="B148" s="0" t="s">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="C148" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D148" s="0" t="s">
+        <x:v>531</x:v>
+      </x:c>
+      <x:c r="E148" s="0" t="s">
+        <x:v>513</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" spans="1:6">
+      <x:c r="A149" s="0" t="s">
+        <x:v>532</x:v>
+      </x:c>
+      <x:c r="B149" s="0" t="s">
+        <x:v>533</x:v>
+      </x:c>
+      <x:c r="C149" s="0" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="D149" s="0" t="s">
+        <x:v>534</x:v>
+      </x:c>
+      <x:c r="E149" s="0" t="s">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" spans="1:6">
+      <x:c r="A150" s="0" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="B150" s="0" t="s">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="C150" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D150" s="0" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="E150" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" spans="1:6">
+      <x:c r="A151" s="0" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="B151" s="0" t="s">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="C151" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D151" s="0" t="s">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="E151" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" spans="1:6">
+      <x:c r="A152" s="0" t="s">
+        <x:v>541</x:v>
+      </x:c>
+      <x:c r="B152" s="0" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="C152" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D152" s="0" t="s">
+        <x:v>543</x:v>
+      </x:c>
+      <x:c r="E152" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" spans="1:6">
+      <x:c r="A153" s="0" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="B153" s="0" t="s">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="C153" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D153" s="0" t="s">
+        <x:v>546</x:v>
+      </x:c>
+      <x:c r="E153" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" spans="1:6">
+      <x:c r="A154" s="0" t="s">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="B154" s="0" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="C154" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D154" s="0" t="s">
+        <x:v>549</x:v>
+      </x:c>
+      <x:c r="E154" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" spans="1:6">
+      <x:c r="A155" s="0" t="s">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="B155" s="0" t="s">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="C155" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="D155" s="0" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="E155" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" spans="1:6">
+      <x:c r="A156" s="0" t="s">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="B156" s="0" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="C156" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D156" s="0" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="E156" s="0" t="s">
+        <x:v>513</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" spans="1:6">
+      <x:c r="A157" s="0" t="s">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="B157" s="0" t="s">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="C157" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D157" s="0" t="s">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="E157" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" spans="1:6">
+      <x:c r="A158" s="0" t="s">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="B158" s="0" t="s">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="C158" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D158" s="0" t="s">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="E158" s="0" t="s">
+        <x:v>562</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" spans="1:6">
+      <x:c r="A159" s="0" t="s">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="B159" s="0" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="C159" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="D159" s="0" t="s">
+        <x:v>565</x:v>
+      </x:c>
+      <x:c r="E159" s="0" t="s">
+        <x:v>566</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" spans="1:6">
+      <x:c r="A160" s="0" t="s">
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="B160" s="0" t="s">
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="C160" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D160" s="0" t="s">
+        <x:v>569</x:v>
+      </x:c>
+      <x:c r="E160" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" spans="1:6">
+      <x:c r="A161" s="0" t="s">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="B161" s="0" t="s">
+        <x:v>571</x:v>
+      </x:c>
+      <x:c r="C161" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D161" s="0" t="s">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="E161" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" spans="1:6">
+      <x:c r="A162" s="0" t="s">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="B162" s="0" t="s">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="C162" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D162" s="0" t="s">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="E162" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" spans="1:6">
+      <x:c r="A163" s="0" t="s">
+        <x:v>576</x:v>
+      </x:c>
+      <x:c r="B163" s="0" t="s">
+        <x:v>577</x:v>
+      </x:c>
+      <x:c r="C163" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D163" s="0" t="s">
+        <x:v>578</x:v>
+      </x:c>
+      <x:c r="E163" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" spans="1:6">
+      <x:c r="A164" s="0" t="s">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="B164" s="0" t="s">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="C164" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D164" s="0" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="E164" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" spans="1:6">
+      <x:c r="A165" s="0" t="s">
+        <x:v>582</x:v>
+      </x:c>
+      <x:c r="B165" s="0" t="s">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="C165" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D165" s="0" t="s">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="E165" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" spans="1:6">
+      <x:c r="A166" s="0" t="s">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c r="B166" s="0" t="s">
+        <x:v>586</x:v>
+      </x:c>
+      <x:c r="C166" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="D166" s="0" t="s">
+        <x:v>587</x:v>
+      </x:c>
+      <x:c r="E166" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" spans="1:6">
+      <x:c r="A167" s="0" t="s">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="B167" s="0" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="C167" s="0" t="s">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="D167" s="0" t="s">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="E167" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" spans="1:6">
+      <x:c r="A168" s="0" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="B168" s="0" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="C168" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D168" s="0" t="s">
+        <x:v>594</x:v>
+      </x:c>
+      <x:c r="E168" s="0" t="s">
+        <x:v>595</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" spans="1:6">
+      <x:c r="A169" s="0" t="s">
+        <x:v>596</x:v>
+      </x:c>
+      <x:c r="B169" s="0" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="C169" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D169" s="0" t="s">
+        <x:v>598</x:v>
+      </x:c>
+      <x:c r="E169" s="0" t="s">
+        <x:v>599</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" spans="1:6">
+      <x:c r="A170" s="0" t="s">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="B170" s="0" t="s">
+        <x:v>601</x:v>
+      </x:c>
+      <x:c r="C170" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D170" s="0" t="s">
+        <x:v>602</x:v>
+      </x:c>
+      <x:c r="E170" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" spans="1:6">
+      <x:c r="A171" s="0" t="s">
+        <x:v>603</x:v>
+      </x:c>
+      <x:c r="B171" s="0" t="s">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="C171" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D171" s="0" t="s">
+        <x:v>605</x:v>
+      </x:c>
+      <x:c r="E171" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" spans="1:6">
+      <x:c r="A172" s="0" t="s">
+        <x:v>606</x:v>
+      </x:c>
+      <x:c r="B172" s="0" t="s">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="C172" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D172" s="0" t="s">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="E172" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" spans="1:6">
+      <x:c r="A173" s="0" t="s">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="B173" s="0" t="s">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="C173" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D173" s="0" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="E173" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" spans="1:6">
+      <x:c r="A174" s="0" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="B174" s="0" t="s">
+        <x:v>612</x:v>
+      </x:c>
+      <x:c r="C174" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D174" s="0" t="s">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="E174" s="0" t="s">
+        <x:v>614</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" spans="1:6">
+      <x:c r="A175" s="0" t="s">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="B175" s="0" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="C175" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D175" s="0" t="s">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="E175" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" spans="1:6">
+      <x:c r="A176" s="0" t="s">
+        <x:v>618</x:v>
+      </x:c>
+      <x:c r="B176" s="0" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="C176" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D176" s="0" t="s">
+        <x:v>620</x:v>
+      </x:c>
+      <x:c r="E176" s="0" t="s">
+        <x:v>524</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" spans="1:6">
+      <x:c r="A177" s="0" t="s">
+        <x:v>621</x:v>
+      </x:c>
+      <x:c r="B177" s="0" t="s">
+        <x:v>622</x:v>
+      </x:c>
+      <x:c r="C177" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D177" s="0" t="s">
+        <x:v>623</x:v>
+      </x:c>
+      <x:c r="E177" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" spans="1:6">
+      <x:c r="A178" s="0" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="B178" s="0" t="s">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="C178" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="D178" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E178" s="0" t="s">
+        <x:v>626</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" spans="1:6">
+      <x:c r="A179" s="0" t="s">
+        <x:v>627</x:v>
+      </x:c>
+      <x:c r="B179" s="0" t="s">
+        <x:v>628</x:v>
+      </x:c>
+      <x:c r="C179" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="D179" s="0" t="s">
+        <x:v>629</x:v>
+      </x:c>
+      <x:c r="E179" s="0" t="s">
+        <x:v>630</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" spans="1:6">
+      <x:c r="A180" s="0" t="s">
+        <x:v>631</x:v>
+      </x:c>
+      <x:c r="B180" s="0" t="s">
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="C180" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D180" s="0" t="s">
+        <x:v>633</x:v>
+      </x:c>
+      <x:c r="E180" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" spans="1:6">
+      <x:c r="A181" s="0" t="s">
+        <x:v>634</x:v>
+      </x:c>
+      <x:c r="B181" s="0" t="s">
+        <x:v>635</x:v>
+      </x:c>
+      <x:c r="C181" s="0" t="s">
+        <x:v>636</x:v>
+      </x:c>
+      <x:c r="D181" s="0" t="s">
+        <x:v>637</x:v>
+      </x:c>
+      <x:c r="E181" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" spans="1:6">
+      <x:c r="A182" s="0" t="s">
+        <x:v>638</x:v>
+      </x:c>
+      <x:c r="B182" s="0" t="s">
+        <x:v>639</x:v>
+      </x:c>
+      <x:c r="C182" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D182" s="0" t="s">
+        <x:v>640</x:v>
+      </x:c>
+      <x:c r="E182" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" spans="1:6">
+      <x:c r="A183" s="0" t="s">
+        <x:v>641</x:v>
+      </x:c>
+      <x:c r="B183" s="0" t="s">
+        <x:v>642</x:v>
+      </x:c>
+      <x:c r="C183" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D183" s="0" t="s">
+        <x:v>643</x:v>
+      </x:c>
+      <x:c r="E183" s="0" t="s">
+        <x:v>644</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" spans="1:6">
+      <x:c r="A184" s="0" t="s">
+        <x:v>645</x:v>
+      </x:c>
+      <x:c r="B184" s="0" t="s">
+        <x:v>646</x:v>
+      </x:c>
+      <x:c r="C184" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D184" s="0" t="s">
+        <x:v>647</x:v>
+      </x:c>
+      <x:c r="E184" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" spans="1:6">
+      <x:c r="A185" s="0" t="s">
+        <x:v>648</x:v>
+      </x:c>
+      <x:c r="B185" s="0" t="s">
+        <x:v>649</x:v>
+      </x:c>
+      <x:c r="C185" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D185" s="0" t="s">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="E185" s="0" t="s">
+        <x:v>566</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" spans="1:6">
+      <x:c r="A186" s="0" t="s">
+        <x:v>651</x:v>
+      </x:c>
+      <x:c r="B186" s="0" t="s">
+        <x:v>652</x:v>
+      </x:c>
+      <x:c r="C186" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D186" s="0" t="s">
+        <x:v>653</x:v>
+      </x:c>
+      <x:c r="E186" s="0" t="s">
+        <x:v>238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" spans="1:6">
+      <x:c r="A187" s="0" t="s">
+        <x:v>654</x:v>
+      </x:c>
+      <x:c r="B187" s="0" t="s">
+        <x:v>655</x:v>
+      </x:c>
+      <x:c r="C187" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="D187" s="0" t="s">
+        <x:v>656</x:v>
+      </x:c>
+      <x:c r="E187" s="0" t="s">
+        <x:v>657</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" spans="1:6">
+      <x:c r="A188" s="0" t="s">
+        <x:v>658</x:v>
+      </x:c>
+      <x:c r="B188" s="0" t="s">
+        <x:v>659</x:v>
+      </x:c>
+      <x:c r="C188" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D188" s="0" t="s">
+        <x:v>660</x:v>
+      </x:c>
+      <x:c r="E188" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" spans="1:6">
+      <x:c r="A189" s="0" t="s">
+        <x:v>661</x:v>
+      </x:c>
+      <x:c r="B189" s="0" t="s">
+        <x:v>662</x:v>
+      </x:c>
+      <x:c r="C189" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D189" s="0" t="s">
+        <x:v>663</x:v>
+      </x:c>
+      <x:c r="E189" s="0" t="s">
+        <x:v>664</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" spans="1:6">
+      <x:c r="A190" s="0" t="s">
+        <x:v>665</x:v>
+      </x:c>
+      <x:c r="B190" s="0" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="C190" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D190" s="0" t="s">
+        <x:v>667</x:v>
+      </x:c>
+      <x:c r="E190" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" spans="1:6">
+      <x:c r="A191" s="0" t="s">
+        <x:v>668</x:v>
+      </x:c>
+      <x:c r="B191" s="0" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="C191" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="D191" s="0" t="s">
+        <x:v>670</x:v>
+      </x:c>
+      <x:c r="E191" s="0" t="s">
+        <x:v>671</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" spans="1:6">
+      <x:c r="A192" s="0" t="s">
+        <x:v>672</x:v>
+      </x:c>
+      <x:c r="B192" s="0" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="C192" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D192" s="0" t="s">
+        <x:v>674</x:v>
+      </x:c>
+      <x:c r="E192" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" spans="1:6">
+      <x:c r="A193" s="0" t="s">
+        <x:v>675</x:v>
+      </x:c>
+      <x:c r="B193" s="0" t="s">
+        <x:v>676</x:v>
+      </x:c>
+      <x:c r="C193" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D193" s="0" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E193" s="0" t="s">
+        <x:v>614</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" spans="1:6">
+      <x:c r="A194" s="0" t="s">
+        <x:v>678</x:v>
+      </x:c>
+      <x:c r="B194" s="0" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="C194" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="D194" s="0" t="s">
+        <x:v>680</x:v>
+      </x:c>
+      <x:c r="E194" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" spans="1:6">
+      <x:c r="A195" s="0" t="s">
+        <x:v>681</x:v>
+      </x:c>
+      <x:c r="B195" s="0" t="s">
+        <x:v>682</x:v>
+      </x:c>
+      <x:c r="C195" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D195" s="0" t="s">
+        <x:v>683</x:v>
+      </x:c>
+      <x:c r="E195" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" spans="1:6">
+      <x:c r="A196" s="0" t="s">
+        <x:v>684</x:v>
+      </x:c>
+      <x:c r="B196" s="0" t="s">
+        <x:v>685</x:v>
+      </x:c>
+      <x:c r="C196" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="D196" s="0" t="s">
+        <x:v>686</x:v>
+      </x:c>
+      <x:c r="E196" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" spans="1:6">
+      <x:c r="A197" s="0" t="s">
+        <x:v>687</x:v>
+      </x:c>
+      <x:c r="B197" s="0" t="s">
+        <x:v>688</x:v>
+      </x:c>
+      <x:c r="C197" s="0" t="s">
+        <x:v>636</x:v>
+      </x:c>
+      <x:c r="D197" s="0" t="s">
+        <x:v>689</x:v>
+      </x:c>
+      <x:c r="E197" s="0" t="s">
+        <x:v>690</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" spans="1:6">
+      <x:c r="A198" s="0" t="s">
+        <x:v>691</x:v>
+      </x:c>
+      <x:c r="B198" s="0" t="s">
+        <x:v>692</x:v>
+      </x:c>
+      <x:c r="C198" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D198" s="0" t="s">
+        <x:v>693</x:v>
+      </x:c>
+      <x:c r="E198" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" spans="1:6">
+      <x:c r="A199" s="0" t="s">
+        <x:v>694</x:v>
+      </x:c>
+      <x:c r="B199" s="0" t="s">
+        <x:v>695</x:v>
+      </x:c>
+      <x:c r="C199" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D199" s="0" t="s">
+        <x:v>696</x:v>
+      </x:c>
+      <x:c r="E199" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" spans="1:6">
+      <x:c r="A200" s="0" t="s">
+        <x:v>697</x:v>
+      </x:c>
+      <x:c r="B200" s="0" t="s">
+        <x:v>698</x:v>
+      </x:c>
+      <x:c r="C200" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D200" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="E200" s="0" t="s">
+        <x:v>699</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" spans="1:6">
+      <x:c r="A201" s="0" t="s">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="B201" s="0" t="s">
+        <x:v>701</x:v>
+      </x:c>
+      <x:c r="C201" s="0" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="D201" s="0" t="s">
+        <x:v>702</x:v>
+      </x:c>
+      <x:c r="E201" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -621,13 +6068,27 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>705</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:4">
+      <x:c r="A2" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>706</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>707</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>708</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -652,60 +6113,60 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="E1" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="F1" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="G1" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>714</x:v>
       </x:c>
       <x:c r="H1" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="I1" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="J1" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="K1" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="L1" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="M1" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="N1" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>721</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:14">
       <x:c r="A2" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>724</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="F2" s="0">
         <x:v>2</x:v>
@@ -719,202 +6180,20 @@
       <x:c r="I2" s="0">
         <x:v>1250</x:v>
       </x:c>
-      <x:c r="J2" s="0" t="s">
-        <x:v>33</x:v>
+      <x:c r="J2" s="0">
+        <x:v>376</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:14">
-      <x:c r="A3" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F3" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G3" s="0">
-        <x:v>1800</x:v>
-      </x:c>
-      <x:c r="H3" s="0">
-        <x:v>900</x:v>
-      </x:c>
-      <x:c r="I3" s="0">
-        <x:v>900</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:14">
-      <x:c r="A4" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F4" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G4" s="0">
-        <x:v>800</x:v>
-      </x:c>
-      <x:c r="H4" s="0">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="I4" s="0">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="M4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:14">
-      <x:c r="A5" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F5" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G5" s="0">
-        <x:v>3500</x:v>
-      </x:c>
-      <x:c r="H5" s="0">
-        <x:v>1750</x:v>
-      </x:c>
-      <x:c r="I5" s="0">
-        <x:v>1750</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="M5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="N5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:C3"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData>
-    <x:row r="1" spans="1:3">
-      <x:c r="A1" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C1" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:3">
-      <x:c r="A2" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B2" s="0">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:3">
-      <x:c r="A3" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B3" s="0">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>728</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/Output_Results.xlsx
+++ b/Data/Output_Results.xlsx
@@ -10,7 +10,6 @@
     <x:sheet name="Accommodation" sheetId="2" r:id="rId5"/>
     <x:sheet name="Weather" sheetId="3" r:id="rId7"/>
     <x:sheet name="Summary" sheetId="4" r:id="rId8"/>
-    <x:sheet name="Errors" sheetId="5" r:id="rId9"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
@@ -110,85 +109,99 @@
     <x:t>Bucuresti</x:t>
   </x:si>
   <x:si>
-    <x:t>Roma</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.06.2026</x:t>
+    <x:t>General Ni</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.01.2026</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cluj</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Viena</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.07.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.07.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Iasi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Brasov</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Timisoara</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Paris</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RowIndex</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ErrorMessage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DepartureDate in the past; ReturnDate in the past; ReturnDate before DepartureDate; </x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DepartureCity missing; Passengers invalid; TotalBudget invalid; DepartureDate in the past; ReturnDate in the past; TransportPreference invalid; </x:t>
-  </x:si>
-  <x:si>
-    <x:t>No weather data</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Insufficient data</x:t>
+    <x:t>Train</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CFR Călători</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6:09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18:16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12 ore 7 min</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://bilete.cfrcalatori.ro/ro-RO/Itineraries/?DepartureStationName=Bucure%C8%99ti%20Nord&amp;ArrivalStationName=General%20Nicolae%20D%C4%83sc%C4%83lescu&amp;DepartureDate=25.01.2026&amp;TimeSelectionId=0&amp;MinutesInDay=0&amp;OrderingTypeId=0&amp;ConnectionsTypeId=1&amp;ChangeStationName=&amp;IsBikesServiceRequired=False&amp;IsOnlineBuyingRequired=False&amp;IsBarRestaurantServiceRequired=False&amp;IsSleeperCouchetteServiceRequired=False
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9:45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20:45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11 ore 0 min</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13:07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22:54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9 ore 47 min</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CFR Călători, Interregional Călători</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16:24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6:38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14 ore 14 min</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://bilete.cfrcalatori.ro/ro-RO/Itineraries/?DepartureStationName=Bucure%C8%99ti%20Nord&amp;ArrivalStationName=R%C4%83zboieni&amp;DepartureDate=25.01.2026&amp;TimeSelectionId=0&amp;MinutesInDay=0&amp;OrderingTypeId=0&amp;ConnectionsTypeId=1&amp;ChangeStationName=&amp;IsBikesServiceRequired=False&amp;IsOnlineBuyingRequired=False&amp;IsBarRestaurantServiceRequired=False&amp;IsSleeperCouchetteServiceRequired=False
+https://interregional.ro/
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18:24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12 ore 14 min</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21:20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7:21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10 ore 1 min</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://bilete.cfrcalatori.ro/ro-RO/Itineraries/?DepartureStationName=Bucure%C8%99ti%20Nord&amp;ArrivalStationName=T%C3%A2rgu%20Mure%C8%99&amp;DepartureDate=25.01.2026&amp;TimeSelectionId=0&amp;MinutesInDay=0&amp;OrderingTypeId=0&amp;ConnectionsTypeId=1&amp;ChangeStationName=&amp;IsBikesServiceRequired=False&amp;IsOnlineBuyingRequired=False&amp;IsBarRestaurantServiceRequired=False&amp;IsSleeperCouchetteServiceRequired=False
+https://interregional.ro/
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7:46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10 ore 26 min</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8:20</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -239,9 +252,13 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="1">
+  <x:cellXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -568,6 +585,214 @@
         <x:v>7</x:v>
       </x:c>
     </x:row>
+    <x:row r="2" spans="1:8">
+      <x:c r="A2" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:8">
+      <x:c r="A3" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H3" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:8">
+      <x:c r="A4" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H4" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:8">
+      <x:c r="A5" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H5" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:8">
+      <x:c r="A6" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H6" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:8">
+      <x:c r="A7" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H7" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:8">
+      <x:c r="A8" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H8" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:8">
+      <x:c r="A9" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H9" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -735,192 +960,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:14">
-      <x:c r="A3" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F3" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G3" s="0">
-        <x:v>1800</x:v>
-      </x:c>
-      <x:c r="H3" s="0">
-        <x:v>900</x:v>
-      </x:c>
-      <x:c r="I3" s="0">
-        <x:v>900</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:14">
-      <x:c r="A4" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F4" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G4" s="0">
-        <x:v>800</x:v>
-      </x:c>
-      <x:c r="H4" s="0">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="I4" s="0">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="M4" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:14">
-      <x:c r="A5" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F5" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G5" s="0">
-        <x:v>3500</x:v>
-      </x:c>
-      <x:c r="H5" s="0">
-        <x:v>1750</x:v>
-      </x:c>
-      <x:c r="I5" s="0">
-        <x:v>1750</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="M5" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="N5" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:C3"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData>
-    <x:row r="1" spans="1:3">
-      <x:c r="A1" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C1" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:3">
-      <x:c r="A2" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B2" s="0">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:3">
-      <x:c r="A3" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B3" s="0">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
